--- a/data/a_Eingangsdaten/EEB_AGEB/Anwendungsbilanzen/EEV-Haushaltsektor nach Anwendungsbereichen 2023.xlsx
+++ b/data/a_Eingangsdaten/EEB_AGEB/Anwendungsbilanzen/EEV-Haushaltsektor nach Anwendungsbereichen 2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\Bedarf\Anwendungsbilanzen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\EEB_AGEB\Anwendungsbilanzen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F0FC1A-752D-4F45-8DC9-546AD4AA6B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAB27BE-59C6-4689-9F7B-A343E4A2CDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{18DBDAD1-78A3-48B9-95EE-91FAA8341C92}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Energieträger</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Wärmepumpe</t>
+  </si>
+  <si>
+    <t>Biomasse</t>
   </si>
 </sst>
 </file>
@@ -460,10 +463,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8B21D2-14CA-4C9D-8270-62E32EF8930C}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +495,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -521,7 +524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -550,7 +553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -579,7 +582,7 @@
         <v>10.444444444444445</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -608,7 +611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -637,7 +640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -666,45 +669,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1">
+        <v>62.81</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3.39</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>20.444444444444443</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="1">
         <v>1.1944444444444444</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -713,17 +737,16 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -732,8 +755,9 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -742,9 +766,9 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -753,9 +777,9 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -764,7 +788,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="2"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
@@ -775,7 +799,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="2"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
@@ -786,40 +810,40 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="2"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
@@ -830,6 +854,28 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
